--- a/email_list.xlsx
+++ b/email_list.xlsx
@@ -1,70 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
-  <si>
-    <t>الإدارة</t>
-  </si>
-  <si>
-    <t>البريد الإلكتروني</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>حالة الإرسال</t>
-  </si>
-  <si>
-    <t>إدارة تقنية المعلومات</t>
-  </si>
-  <si>
-    <t>إدارة الشؤون الإدارية</t>
-  </si>
-  <si>
-    <t>إدارة الرقابة المالية</t>
-  </si>
-  <si>
-    <t>it@example.gov.sa</t>
-  </si>
-  <si>
-    <t>admin@example.gov.sa</t>
-  </si>
-  <si>
-    <t>finance@example.gov.sa</t>
-  </si>
-  <si>
-    <t>فعال</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -83,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -377,58 +408,793 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>الإدارة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>البريد الإلكتروني</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>حالة الإرسال</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>إدارة الاستثمار - غرب</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>iws@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ادارة الرخص التجارية والاستثمارية - جنوب</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>South.CL@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ادارة الرخص التجارية والاستثمارية - شرق</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>East.CL@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ادارة الرخص التجارية والاستثمارية - غرب</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>West.CL@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ادارة الرخص التجارية والاستثمارية - وسط</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Central.CL@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>إدارة الرقابة العمرانية - غرب</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>إدارة المساحة</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SURV@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>إدارة المنح (إدارة بيانات المنح)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grantdata@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ادارة رخص البناء</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bpermits@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>إدارة رخص البناء - جنوب</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>South.BL@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>إدارة رخص البناء - شرق</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>East.BL@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>إدارة رخص البناء - شمال</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>North.BL@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>إدارة رخص البناء - غرب</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>West.BL@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>إدارة رخص البناء - وسط</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Central.BL@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الأراضي - جنوب</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>South.Land@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الأراضي - شمال</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>North.Land@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الأراضي - غرب</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>West.Land@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>إدارة شؤون الأراضي - وسط</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Central.Land@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>الادارة العامة للأراضي</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>الإدارة العامة للبيانات الجغرافية</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Geospatial@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>الادارة العامة للتخطيط العمراني</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>upa@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>فريق التحقق النهائي للشكاوى</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>فريق الشكاوى و الطلبات</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>فريق مشرف مركز الاتصال</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>مدير إدارة الاستثمار – غرب (إدارة الاستثمار قطاع غرب)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>iws@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>مدير إدارة التعويضات (إدارة التعويضات)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Comp@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>مدير ادارة الرخص التجارية والاستثمارية - غرب</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>مدير إدارة المنح</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>مدير إدارة شؤون الأراضي - غرب</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>مدير الادارة العامة للأراضي (الإدارة العامة للأراضي و المساحة)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>landpt@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>مدير الإدارة العامة للبيانات الجغرافية (الإدارة العامة للبيانات الجغرافية)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Geospatial@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>مدير النظام</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي الحائر - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AlHairOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي الخليج - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AlKhaleejOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي السلام - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AlSalamOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي العقيق - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AlAqiqOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي المعذر - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AlMaatharOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي المغرزات - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AlMughrizatOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي المنصورة - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AlMansouraOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي النفل - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AlNafalOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي طويق - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TuwaiqOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي ظهرة لبن - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DhahratLabanOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي عكاظ - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>OkazOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>مكتب مدينتي قرطبة - المسؤول المختص</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>QurtubahOfficee@alriyadh.gov.sa</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>فعال</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>